--- a/Experiments/outputs/scenario_4_np.xlsx
+++ b/Experiments/outputs/scenario_4_np.xlsx
@@ -530,55 +530,55 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>465.7155686043159</v>
+        <v>515.4248245901433</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06810903549194336</v>
+        <v>0.1072051525115967</v>
       </c>
       <c r="E2" t="n">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>559.9698954275138</v>
+        <v>553.7879669321328</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1549868583679199</v>
+        <v>0.5161950588226318</v>
       </c>
       <c r="J2" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="L2" t="n">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="M2" t="n">
-        <v>1079.18534868299</v>
+        <v>1083.278390087654</v>
       </c>
       <c r="N2" t="n">
-        <v>1.422260046005249</v>
+        <v>1.877549886703491</v>
       </c>
       <c r="O2" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="P2" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Q2" t="n">
-        <v>850</v>
+        <v>752</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5684563646340612</v>
+        <v>0.5241991077211118</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4811179598473178</v>
+        <v>0.4887851802459359</v>
       </c>
     </row>
     <row r="3">
@@ -591,55 +591,55 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>376.98189110777</v>
+        <v>430.5836602139894</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07851982116699219</v>
+        <v>0.1326839923858643</v>
       </c>
       <c r="E3" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G3" t="n">
         <v>5</v>
       </c>
-      <c r="G3" t="n">
-        <v>9</v>
-      </c>
       <c r="H3" t="n">
-        <v>537.6118087661166</v>
+        <v>495.025538986961</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2662057876586914</v>
+        <v>0.4036600589752197</v>
       </c>
       <c r="J3" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K3" t="n">
         <v>11</v>
       </c>
       <c r="L3" t="n">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="M3" t="n">
-        <v>1094.468803986438</v>
+        <v>1075.005514316436</v>
       </c>
       <c r="N3" t="n">
-        <v>1.469588994979858</v>
+        <v>1.441874980926514</v>
       </c>
       <c r="O3" t="n">
-        <v>311</v>
+        <v>340</v>
       </c>
       <c r="P3" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="Q3" t="n">
-        <v>804</v>
+        <v>870</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6555572075378758</v>
+        <v>0.5994591148792526</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5087920214738453</v>
+        <v>0.5395134886338391</v>
       </c>
     </row>
     <row r="4">
@@ -652,55 +652,55 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>487.5104954819253</v>
+        <v>515.441446124843</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0590968132019043</v>
+        <v>0.08877110481262207</v>
       </c>
       <c r="E4" t="n">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>550.8680052130504</v>
+        <v>558.2870605781395</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2379829883575439</v>
+        <v>0.4032831192016602</v>
       </c>
       <c r="J4" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="K4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L4" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="M4" t="n">
-        <v>1083.849886563756</v>
+        <v>1095.600735384674</v>
       </c>
       <c r="N4" t="n">
-        <v>1.707128047943115</v>
+        <v>2.265025854110718</v>
       </c>
       <c r="O4" t="n">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="P4" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="Q4" t="n">
-        <v>809</v>
+        <v>823</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5502047824837337</v>
+        <v>0.5295353229715863</v>
       </c>
       <c r="S4" t="n">
-        <v>0.491748800233282</v>
+        <v>0.4904283626807528</v>
       </c>
     </row>
     <row r="5">
@@ -713,55 +713,55 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>434.8860917739306</v>
+        <v>538.0133360147846</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07533693313598633</v>
+        <v>0.1997201442718506</v>
       </c>
       <c r="E5" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>516.7587416073138</v>
+        <v>465.8535693963374</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2124881744384766</v>
+        <v>0.8574221134185791</v>
       </c>
       <c r="J5" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L5" t="n">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="M5" t="n">
-        <v>1111.770139079765</v>
+        <v>1092.576667457175</v>
       </c>
       <c r="N5" t="n">
-        <v>1.773061752319336</v>
+        <v>1.859004974365234</v>
       </c>
       <c r="O5" t="n">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="P5" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Q5" t="n">
-        <v>837</v>
+        <v>885</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6088345274915418</v>
+        <v>0.5075738371139314</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5351928213910786</v>
+        <v>0.5736193319224462</v>
       </c>
     </row>
     <row r="6">
@@ -774,55 +774,55 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>586.7388761131635</v>
+        <v>495.1132856794808</v>
       </c>
       <c r="D6" t="n">
-        <v>0.09159994125366211</v>
+        <v>0.1439418792724609</v>
       </c>
       <c r="E6" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" t="n">
+        <v>491.8711052547435</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7793340682983398</v>
+      </c>
+      <c r="J6" t="n">
+        <v>96</v>
+      </c>
+      <c r="K6" t="n">
         <v>11</v>
       </c>
-      <c r="G6" t="n">
-        <v>4</v>
-      </c>
-      <c r="H6" t="n">
-        <v>554.3528972940287</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.295773983001709</v>
-      </c>
-      <c r="J6" t="n">
-        <v>97</v>
-      </c>
-      <c r="K6" t="n">
-        <v>12</v>
-      </c>
       <c r="L6" t="n">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="M6" t="n">
-        <v>1125.182363287882</v>
+        <v>1106.667564507828</v>
       </c>
       <c r="N6" t="n">
-        <v>1.466932773590088</v>
+        <v>2.640756130218506</v>
       </c>
       <c r="O6" t="n">
-        <v>327</v>
+        <v>354</v>
       </c>
       <c r="P6" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="Q6" t="n">
-        <v>832</v>
+        <v>915</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4785388615595955</v>
+        <v>0.5526088397651067</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5073217325641677</v>
+        <v>0.5555385184949421</v>
       </c>
     </row>
     <row r="7">
@@ -835,55 +835,55 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>640.516179023273</v>
+        <v>423.3291006188389</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1617920398712158</v>
+        <v>0.1779270172119141</v>
       </c>
       <c r="E7" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="F7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7</v>
+      </c>
+      <c r="H7" t="n">
+        <v>568.4893503203346</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.4645810127258301</v>
+      </c>
+      <c r="J7" t="n">
+        <v>82</v>
+      </c>
+      <c r="K7" t="n">
         <v>16</v>
       </c>
-      <c r="G7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H7" t="n">
-        <v>520.8836914469214</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.3704230785369873</v>
-      </c>
-      <c r="J7" t="n">
-        <v>90</v>
-      </c>
-      <c r="K7" t="n">
-        <v>12</v>
-      </c>
       <c r="L7" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="M7" t="n">
-        <v>1092.600198202457</v>
+        <v>1117.871968954646</v>
       </c>
       <c r="N7" t="n">
-        <v>1.409111022949219</v>
+        <v>1.513067960739136</v>
       </c>
       <c r="O7" t="n">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="P7" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="Q7" t="n">
-        <v>882</v>
+        <v>850</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4137689338908702</v>
+        <v>0.6213080635569509</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5232623128717369</v>
+        <v>0.4914539713774689</v>
       </c>
     </row>
     <row r="8">
@@ -896,55 +896,55 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>664.3437912083417</v>
+        <v>602.4277095168586</v>
       </c>
       <c r="D8" t="n">
-        <v>0.07971620559692383</v>
+        <v>0.1014180183410645</v>
       </c>
       <c r="E8" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="F8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>523.7258186587434</v>
+        <v>593.0961390393395</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2182037830352783</v>
+        <v>0.5592820644378662</v>
       </c>
       <c r="J8" t="n">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="K8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L8" t="n">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="M8" t="n">
-        <v>1099.01180533662</v>
+        <v>1128.445766301045</v>
       </c>
       <c r="N8" t="n">
-        <v>1.596848964691162</v>
+        <v>1.361873865127563</v>
       </c>
       <c r="O8" t="n">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="P8" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Q8" t="n">
-        <v>699</v>
+        <v>742</v>
       </c>
       <c r="R8" t="n">
-        <v>0.395508048246254</v>
+        <v>0.4661438524497561</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5234575132718166</v>
+        <v>0.4744132533870358</v>
       </c>
     </row>
     <row r="9">
@@ -957,55 +957,55 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>495.7537050899826</v>
+        <v>513.804487002801</v>
       </c>
       <c r="D9" t="n">
-        <v>0.08888506889343262</v>
+        <v>0.09496188163757324</v>
       </c>
       <c r="E9" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>646.0464830315651</v>
+        <v>469.711046973869</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1933400630950928</v>
+        <v>0.4545269012451172</v>
       </c>
       <c r="J9" t="n">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="K9" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="L9" t="n">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="M9" t="n">
-        <v>1117.957343010342</v>
+        <v>1106.182783476535</v>
       </c>
       <c r="N9" t="n">
-        <v>1.523962736129761</v>
+        <v>1.278053760528564</v>
       </c>
       <c r="O9" t="n">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="P9" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="Q9" t="n">
-        <v>797</v>
+        <v>841</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5565540061170327</v>
+        <v>0.5355157441629989</v>
       </c>
       <c r="S9" t="n">
-        <v>0.422118842842478</v>
+        <v>0.5753766430013936</v>
       </c>
     </row>
     <row r="10">
@@ -1018,55 +1018,55 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>641.9815557601953</v>
+        <v>434.9022315611868</v>
       </c>
       <c r="D10" t="n">
-        <v>0.05686521530151367</v>
+        <v>0.09117603302001953</v>
       </c>
       <c r="E10" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>516.3858369740713</v>
+        <v>582.8277245818952</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1458828449249268</v>
+        <v>0.4383938312530518</v>
       </c>
       <c r="J10" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K10" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L10" t="n">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="M10" t="n">
-        <v>1080.360981364333</v>
+        <v>1057.856864841701</v>
       </c>
       <c r="N10" t="n">
-        <v>1.413578033447266</v>
+        <v>1.631323099136353</v>
       </c>
       <c r="O10" t="n">
-        <v>304</v>
+        <v>329</v>
       </c>
       <c r="P10" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q10" t="n">
-        <v>765</v>
+        <v>807</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4057712497636953</v>
+        <v>0.5888836703571745</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5220247251784734</v>
+        <v>0.4490485963154287</v>
       </c>
     </row>
     <row r="11">
@@ -1079,55 +1079,55 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>553.651916929476</v>
+        <v>580.484354538007</v>
       </c>
       <c r="D11" t="n">
-        <v>0.05993199348449707</v>
+        <v>0.1156768798828125</v>
       </c>
       <c r="E11" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="F11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>587.024309925063</v>
+        <v>520.3543559654681</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1960277557373047</v>
+        <v>0.6706349849700928</v>
       </c>
       <c r="J11" t="n">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="K11" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>114</v>
+        <v>147</v>
       </c>
       <c r="M11" t="n">
-        <v>1114.770730649355</v>
+        <v>1066.270309192076</v>
       </c>
       <c r="N11" t="n">
-        <v>1.393929958343506</v>
+        <v>1.557867050170898</v>
       </c>
       <c r="O11" t="n">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="P11" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q11" t="n">
-        <v>827</v>
+        <v>770</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5033490728564668</v>
+        <v>0.455593624305411</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4734125199150853</v>
+        <v>0.5119864527037746</v>
       </c>
     </row>
     <row r="12">
@@ -1140,55 +1140,55 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>561.3238997139223</v>
+        <v>534.290397847869</v>
       </c>
       <c r="D12" t="n">
-        <v>0.05954098701477051</v>
+        <v>0.09704208374023438</v>
       </c>
       <c r="E12" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>493.0601849368962</v>
+        <v>574.6909104730016</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1894221305847168</v>
+        <v>0.4870889186859131</v>
       </c>
       <c r="J12" t="n">
         <v>103</v>
       </c>
       <c r="K12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L12" t="n">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="M12" t="n">
-        <v>1085.553334389725</v>
+        <v>1099.158465410935</v>
       </c>
       <c r="N12" t="n">
-        <v>1.266655921936035</v>
+        <v>1.33579421043396</v>
       </c>
       <c r="O12" t="n">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="P12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="Q12" t="n">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4829144898444932</v>
+        <v>0.5139095820472823</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5457982861670411</v>
+        <v>0.4771537239099132</v>
       </c>
     </row>
     <row r="13">
@@ -1201,55 +1201,55 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>595.7117871486358</v>
+        <v>462.425518969517</v>
       </c>
       <c r="D13" t="n">
-        <v>0.04749202728271484</v>
+        <v>0.1050040721893311</v>
       </c>
       <c r="E13" t="n">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="F13" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>625.1142536088767</v>
+        <v>459.9809875695899</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1451699733734131</v>
+        <v>0.3613851070404053</v>
       </c>
       <c r="J13" t="n">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="K13" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L13" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="M13" t="n">
-        <v>1127.492911182388</v>
+        <v>1119.086498002549</v>
       </c>
       <c r="N13" t="n">
-        <v>1.816869974136353</v>
+        <v>1.29849100112915</v>
       </c>
       <c r="O13" t="n">
-        <v>301</v>
+        <v>344</v>
       </c>
       <c r="P13" t="n">
         <v>37</v>
       </c>
       <c r="Q13" t="n">
-        <v>729</v>
+        <v>885</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4716491950943441</v>
+        <v>0.5867830415299462</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4455714555638961</v>
+        <v>0.58896744050562</v>
       </c>
     </row>
     <row r="14">
@@ -1262,55 +1262,55 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>590.9044237459655</v>
+        <v>597.7726080689591</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0874030590057373</v>
+        <v>0.0986781120300293</v>
       </c>
       <c r="E14" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F14" t="n">
         <v>15</v>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H14" t="n">
-        <v>491.5262190656812</v>
+        <v>612.7847456934094</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2617158889770508</v>
+        <v>0.2732570171356201</v>
       </c>
       <c r="J14" t="n">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="K14" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="L14" t="n">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="M14" t="n">
-        <v>1108.835778502995</v>
+        <v>1064.978528282317</v>
       </c>
       <c r="N14" t="n">
-        <v>1.465683937072754</v>
+        <v>1.566705226898193</v>
       </c>
       <c r="O14" t="n">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="P14" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q14" t="n">
-        <v>785</v>
+        <v>813</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4670947355759684</v>
+        <v>0.4386998496269262</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5567186515849302</v>
+        <v>0.4246036615576108</v>
       </c>
     </row>
     <row r="15">
@@ -1323,55 +1323,55 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>482.8061472742573</v>
+        <v>500.6255464420145</v>
       </c>
       <c r="D15" t="n">
-        <v>0.05658698081970215</v>
+        <v>0.1082539558410645</v>
       </c>
       <c r="E15" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="F15" t="n">
         <v>10</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
-        <v>528.7512272890854</v>
+        <v>511.3949167115418</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1828849315643311</v>
+        <v>0.5405828952789307</v>
       </c>
       <c r="J15" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L15" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="M15" t="n">
-        <v>1081.827077240661</v>
+        <v>1053.356537487896</v>
       </c>
       <c r="N15" t="n">
-        <v>1.496454954147339</v>
+        <v>1.537585973739624</v>
       </c>
       <c r="O15" t="n">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="P15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q15" t="n">
-        <v>795</v>
+        <v>788</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5537122730319191</v>
+        <v>0.5247330522712336</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5112423802168705</v>
+        <v>0.5145091917964025</v>
       </c>
     </row>
     <row r="16">
@@ -1384,55 +1384,55 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>600.7533720273466</v>
+        <v>538.4294416153275</v>
       </c>
       <c r="D16" t="n">
-        <v>0.07145810127258301</v>
+        <v>0.09872293472290039</v>
       </c>
       <c r="E16" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F16" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>533.7279468044342</v>
+        <v>555.2950747059025</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1782240867614746</v>
+        <v>0.5155332088470459</v>
       </c>
       <c r="J16" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="K16" t="n">
         <v>13</v>
       </c>
       <c r="L16" t="n">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="M16" t="n">
-        <v>1123.359210063612</v>
+        <v>1077.382725026268</v>
       </c>
       <c r="N16" t="n">
-        <v>1.427248001098633</v>
+        <v>1.425566911697388</v>
       </c>
       <c r="O16" t="n">
-        <v>306</v>
+        <v>346</v>
       </c>
       <c r="P16" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="Q16" t="n">
-        <v>793</v>
+        <v>865</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4652170324100266</v>
+        <v>0.5002431084996282</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5248822086265611</v>
+        <v>0.4845888449785904</v>
       </c>
     </row>
     <row r="17">
@@ -1445,55 +1445,55 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>479.9817465970839</v>
+        <v>404.1644486554916</v>
       </c>
       <c r="D17" t="n">
-        <v>0.05995917320251465</v>
+        <v>0.09921598434448242</v>
       </c>
       <c r="E17" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>512.2957846968171</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.3967270851135254</v>
+      </c>
+      <c r="J17" t="n">
+        <v>93</v>
+      </c>
+      <c r="K17" t="n">
         <v>11</v>
       </c>
-      <c r="G17" t="n">
-        <v>8</v>
-      </c>
-      <c r="H17" t="n">
-        <v>485.9830628671112</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.1965420246124268</v>
-      </c>
-      <c r="J17" t="n">
-        <v>108</v>
-      </c>
-      <c r="K17" t="n">
-        <v>8</v>
-      </c>
       <c r="L17" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="M17" t="n">
-        <v>1118.165830423022</v>
+        <v>1078.243767109041</v>
       </c>
       <c r="N17" t="n">
-        <v>1.367280960083008</v>
+        <v>1.370495796203613</v>
       </c>
       <c r="O17" t="n">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="P17" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="Q17" t="n">
-        <v>895</v>
+        <v>789</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5707418939680009</v>
+        <v>0.6251641224515243</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5653747864185269</v>
+        <v>0.5248794379119193</v>
       </c>
     </row>
     <row r="18">
@@ -1506,55 +1506,55 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>456.4699436113374</v>
+        <v>402.8653681905411</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0565340518951416</v>
+        <v>0.09672093391418457</v>
       </c>
       <c r="E18" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G18" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>532.4527998428712</v>
+        <v>505.1227156279455</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2193429470062256</v>
+        <v>0.4063689708709717</v>
       </c>
       <c r="J18" t="n">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="K18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L18" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="M18" t="n">
-        <v>1158.451757469642</v>
+        <v>1053.80405811704</v>
       </c>
       <c r="N18" t="n">
-        <v>1.694025993347168</v>
+        <v>1.515233993530273</v>
       </c>
       <c r="O18" t="n">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="P18" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="Q18" t="n">
-        <v>754</v>
+        <v>775</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6059655133085684</v>
+        <v>0.6177037229194301</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5403755085961581</v>
+        <v>0.5206673273487772</v>
       </c>
     </row>
     <row r="19">
@@ -1567,55 +1567,55 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>604.5143322836229</v>
+        <v>506.5708652719101</v>
       </c>
       <c r="D19" t="n">
-        <v>0.06868314743041992</v>
+        <v>0.1305720806121826</v>
       </c>
       <c r="E19" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="F19" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H19" t="n">
-        <v>568.9578366860571</v>
+        <v>564.6559750147244</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2118010520935059</v>
+        <v>0.4934549331665039</v>
       </c>
       <c r="J19" t="n">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="K19" t="n">
         <v>12</v>
       </c>
       <c r="L19" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="M19" t="n">
-        <v>1117.183421239158</v>
+        <v>1146.479662619629</v>
       </c>
       <c r="N19" t="n">
-        <v>1.552474021911621</v>
+        <v>1.52350378036499</v>
       </c>
       <c r="O19" t="n">
-        <v>319</v>
+        <v>343</v>
       </c>
       <c r="P19" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q19" t="n">
-        <v>784</v>
+        <v>867</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4588942864788422</v>
+        <v>0.5581510237046597</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4907211959384609</v>
+        <v>0.5074871422276052</v>
       </c>
     </row>
     <row r="20">
@@ -1628,55 +1628,55 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>478.4669414222493</v>
+        <v>515.5360483600524</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0711219310760498</v>
+        <v>0.1146039962768555</v>
       </c>
       <c r="E20" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G20" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>494.9564551408732</v>
+        <v>553.9377259425612</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1773209571838379</v>
+        <v>0.4699501991271973</v>
       </c>
       <c r="J20" t="n">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="K20" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L20" t="n">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="M20" t="n">
-        <v>1124.96741444706</v>
+        <v>1112.80000817244</v>
       </c>
       <c r="N20" t="n">
-        <v>1.744501113891602</v>
+        <v>1.301292181015015</v>
       </c>
       <c r="O20" t="n">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="P20" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="Q20" t="n">
-        <v>750</v>
+        <v>767</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5746837328106753</v>
+        <v>0.5367217428343469</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5600259627216378</v>
+        <v>0.5022126870287345</v>
       </c>
     </row>
     <row r="21">
@@ -1689,55 +1689,55 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>596.414543051431</v>
+        <v>593.0804582414204</v>
       </c>
       <c r="D21" t="n">
-        <v>0.06473922729492188</v>
+        <v>0.08616185188293457</v>
       </c>
       <c r="E21" t="n">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="F21" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G21" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>634.8498716847</v>
+        <v>558.6033014374091</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1442618370056152</v>
+        <v>0.3288557529449463</v>
       </c>
       <c r="J21" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="K21" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L21" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="M21" t="n">
-        <v>1058.984435798532</v>
+        <v>1140.757676509801</v>
       </c>
       <c r="N21" t="n">
-        <v>1.542212724685669</v>
+        <v>1.291955232620239</v>
       </c>
       <c r="O21" t="n">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P21" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="Q21" t="n">
-        <v>883</v>
+        <v>817</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4368051853361735</v>
+        <v>0.4800995246808452</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4005106683121469</v>
+        <v>0.5103225575948078</v>
       </c>
     </row>
     <row r="22">
@@ -1750,55 +1750,55 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>437.7956301117556</v>
+        <v>611.195884977628</v>
       </c>
       <c r="D22" t="n">
-        <v>0.07608413696289062</v>
+        <v>0.09531521797180176</v>
       </c>
       <c r="E22" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F22" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H22" t="n">
-        <v>495.1261650980033</v>
+        <v>524.5716165457241</v>
       </c>
       <c r="I22" t="n">
-        <v>0.29386305809021</v>
+        <v>0.2704260349273682</v>
       </c>
       <c r="J22" t="n">
+        <v>74</v>
+      </c>
+      <c r="K22" t="n">
+        <v>18</v>
+      </c>
+      <c r="L22" t="n">
         <v>90</v>
       </c>
-      <c r="K22" t="n">
-        <v>11</v>
-      </c>
-      <c r="L22" t="n">
-        <v>98</v>
-      </c>
       <c r="M22" t="n">
-        <v>1104.397738899459</v>
+        <v>1056.861261580712</v>
       </c>
       <c r="N22" t="n">
-        <v>1.917894840240479</v>
+        <v>1.418294906616211</v>
       </c>
       <c r="O22" t="n">
-        <v>302</v>
+        <v>340</v>
       </c>
       <c r="P22" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="Q22" t="n">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6035888025739509</v>
+        <v>0.4216876829570963</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5516776722203357</v>
+        <v>0.5036513915164799</v>
       </c>
     </row>
     <row r="23">
@@ -1811,55 +1811,55 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>509.6563154605407</v>
+        <v>404.2575567191808</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1022069454193115</v>
+        <v>0.1215291023254395</v>
       </c>
       <c r="E23" t="n">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="F23" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H23" t="n">
-        <v>536.8354954980404</v>
+        <v>529.4165574340717</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3367202281951904</v>
+        <v>0.3951396942138672</v>
       </c>
       <c r="J23" t="n">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="K23" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="L23" t="n">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="M23" t="n">
-        <v>1077.328421704061</v>
+        <v>1052.595982894363</v>
       </c>
       <c r="N23" t="n">
-        <v>1.840837955474854</v>
+        <v>1.44558310508728</v>
       </c>
       <c r="O23" t="n">
-        <v>313</v>
+        <v>341</v>
       </c>
       <c r="P23" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="Q23" t="n">
-        <v>740</v>
+        <v>845</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5269257682310161</v>
+        <v>0.6159423337265849</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5016974539213379</v>
+        <v>0.4970372621237688</v>
       </c>
     </row>
     <row r="24">
@@ -1872,55 +1872,55 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>450.7810155220572</v>
+        <v>527.4342056087544</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1715929508209229</v>
+        <v>0.1123552322387695</v>
       </c>
       <c r="E24" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="F24" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G24" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H24" t="n">
-        <v>486.8739621549685</v>
+        <v>531.8545984917736</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3974921703338623</v>
+        <v>0.5962588787078857</v>
       </c>
       <c r="J24" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="K24" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L24" t="n">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="M24" t="n">
-        <v>1113.299519986208</v>
+        <v>1101.872772044339</v>
       </c>
       <c r="N24" t="n">
-        <v>1.803336143493652</v>
+        <v>1.383355855941772</v>
       </c>
       <c r="O24" t="n">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="P24" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="Q24" t="n">
-        <v>885</v>
+        <v>861</v>
       </c>
       <c r="R24" t="n">
-        <v>0.5950945747936354</v>
+        <v>0.5213293049884615</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5626747758222334</v>
+        <v>0.5173175960188153</v>
       </c>
     </row>
     <row r="25">
@@ -1933,55 +1933,55 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>675.8703758088724</v>
+        <v>559.8769161050426</v>
       </c>
       <c r="D25" t="n">
-        <v>0.06814908981323242</v>
+        <v>0.1072471141815186</v>
       </c>
       <c r="E25" t="n">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="F25" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H25" t="n">
-        <v>518.1019388007529</v>
+        <v>600.7248080416884</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2688479423522949</v>
+        <v>0.5034768581390381</v>
       </c>
       <c r="J25" t="n">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="K25" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L25" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="M25" t="n">
-        <v>1096.616666540226</v>
+        <v>1116.678144302277</v>
       </c>
       <c r="N25" t="n">
-        <v>1.444047927856445</v>
+        <v>1.27845287322998</v>
       </c>
       <c r="O25" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P25" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="Q25" t="n">
-        <v>842</v>
+        <v>833</v>
       </c>
       <c r="R25" t="n">
-        <v>0.3836767245739463</v>
+        <v>0.498622840465043</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5275450806020117</v>
+        <v>0.4620430147157278</v>
       </c>
     </row>
     <row r="26">
@@ -1994,55 +1994,55 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>600.6187923040603</v>
+        <v>637.6491099121498</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08544182777404785</v>
+        <v>0.07234311103820801</v>
       </c>
       <c r="E26" t="n">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="F26" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H26" t="n">
-        <v>604.9797303226624</v>
+        <v>621.101101146692</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3593480587005615</v>
+        <v>0.4124181270599365</v>
       </c>
       <c r="J26" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="K26" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L26" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="M26" t="n">
-        <v>1109.656371501392</v>
+        <v>1075.616092531745</v>
       </c>
       <c r="N26" t="n">
-        <v>1.535892009735107</v>
+        <v>1.459800958633423</v>
       </c>
       <c r="O26" t="n">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="P26" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="Q26" t="n">
-        <v>910</v>
+        <v>892</v>
       </c>
       <c r="R26" t="n">
-        <v>0.4587344265041181</v>
+        <v>0.407177789232146</v>
       </c>
       <c r="S26" t="n">
-        <v>0.4548044368869706</v>
+        <v>0.4225624686548085</v>
       </c>
     </row>
     <row r="27">
@@ -2055,55 +2055,55 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>529.4652607097534</v>
+        <v>539.1376688903207</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0649268627166748</v>
+        <v>0.1427631378173828</v>
       </c>
       <c r="E27" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H27" t="n">
-        <v>582.2124692633449</v>
+        <v>523.8174548944767</v>
       </c>
       <c r="I27" t="n">
-        <v>0.188101053237915</v>
+        <v>0.5914089679718018</v>
       </c>
       <c r="J27" t="n">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="K27" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L27" t="n">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="M27" t="n">
-        <v>1125.784098244844</v>
+        <v>1102.581003566839</v>
       </c>
       <c r="N27" t="n">
-        <v>1.367926120758057</v>
+        <v>1.44608736038208</v>
       </c>
       <c r="O27" t="n">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="P27" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="Q27" t="n">
-        <v>822</v>
+        <v>756</v>
       </c>
       <c r="R27" t="n">
-        <v>0.5296920061890932</v>
+        <v>0.511022167853232</v>
       </c>
       <c r="S27" t="n">
-        <v>0.4828382545365096</v>
+        <v>0.5249170326715838</v>
       </c>
     </row>
     <row r="28">
@@ -2116,55 +2116,55 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>498.277034425915</v>
+        <v>542.7545160760424</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08246898651123047</v>
+        <v>0.08653402328491211</v>
       </c>
       <c r="E28" t="n">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G28" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H28" t="n">
-        <v>510.9488178736295</v>
+        <v>500.3482847269996</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2126908302307129</v>
+        <v>0.491361141204834</v>
       </c>
       <c r="J28" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="K28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L28" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M28" t="n">
-        <v>1097.853394427275</v>
+        <v>1078.917418862799</v>
       </c>
       <c r="N28" t="n">
-        <v>1.283010005950928</v>
+        <v>1.335251808166504</v>
       </c>
       <c r="O28" t="n">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="P28" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q28" t="n">
-        <v>880</v>
+        <v>814</v>
       </c>
       <c r="R28" t="n">
-        <v>0.5461351789271877</v>
+        <v>0.4969452651453931</v>
       </c>
       <c r="S28" t="n">
-        <v>0.5345928514069226</v>
+        <v>0.53624969253497</v>
       </c>
     </row>
     <row r="29">
@@ -2177,55 +2177,55 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>544.6919235951183</v>
+        <v>618.8684057407385</v>
       </c>
       <c r="D29" t="n">
-        <v>0.05452990531921387</v>
+        <v>0.1028280258178711</v>
       </c>
       <c r="E29" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F29" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G29" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>524.0489705595571</v>
+        <v>529.9134401181757</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1544229984283447</v>
+        <v>0.4614861011505127</v>
       </c>
       <c r="J29" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K29" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L29" t="n">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="M29" t="n">
-        <v>1097.84264252654</v>
+        <v>1091.992158496924</v>
       </c>
       <c r="N29" t="n">
-        <v>1.260968923568726</v>
+        <v>1.360807180404663</v>
       </c>
       <c r="O29" t="n">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="P29" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q29" t="n">
-        <v>768</v>
+        <v>853</v>
       </c>
       <c r="R29" t="n">
-        <v>0.5038524625518448</v>
+        <v>0.4332666210785049</v>
       </c>
       <c r="S29" t="n">
-        <v>0.5226556609665595</v>
+        <v>0.5147277972695548</v>
       </c>
     </row>
     <row r="30">
@@ -2238,55 +2238,55 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>654.6587952879333</v>
+        <v>466.9470425975416</v>
       </c>
       <c r="D30" t="n">
-        <v>0.05058908462524414</v>
+        <v>0.0966799259185791</v>
       </c>
       <c r="E30" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="F30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H30" t="n">
-        <v>491.2329736023705</v>
+        <v>494.8008197272575</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1503019332885742</v>
+        <v>0.4233829975128174</v>
       </c>
       <c r="J30" t="n">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="K30" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L30" t="n">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="M30" t="n">
-        <v>1064.943456138825</v>
+        <v>1085.573724835946</v>
       </c>
       <c r="N30" t="n">
-        <v>1.226364135742188</v>
+        <v>1.292464017868042</v>
       </c>
       <c r="O30" t="n">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="P30" t="n">
         <v>34</v>
       </c>
       <c r="Q30" t="n">
-        <v>777</v>
+        <v>852</v>
       </c>
       <c r="R30" t="n">
-        <v>0.3852642677748024</v>
+        <v>0.5698615101723213</v>
       </c>
       <c r="S30" t="n">
-        <v>0.5387238911411896</v>
+        <v>0.5442033936460345</v>
       </c>
     </row>
     <row r="31">
@@ -2299,55 +2299,55 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>652.1028496176467</v>
+        <v>429.2685761843894</v>
       </c>
       <c r="D31" t="n">
-        <v>0.06657576560974121</v>
+        <v>0.1094980239868164</v>
       </c>
       <c r="E31" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="F31" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H31" t="n">
-        <v>568.7435575729386</v>
+        <v>491.2332848568453</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1528360843658447</v>
+        <v>0.4601280689239502</v>
       </c>
       <c r="J31" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="K31" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L31" t="n">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="M31" t="n">
-        <v>1054.47165327811</v>
+        <v>1099.809256604671</v>
       </c>
       <c r="N31" t="n">
-        <v>1.405781984329224</v>
+        <v>1.497200965881348</v>
       </c>
       <c r="O31" t="n">
-        <v>295</v>
+        <v>329</v>
       </c>
       <c r="P31" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q31" t="n">
-        <v>744</v>
+        <v>860</v>
       </c>
       <c r="R31" t="n">
-        <v>0.381583328873366</v>
+        <v>0.6096881585543057</v>
       </c>
       <c r="S31" t="n">
-        <v>0.4606364658501291</v>
+        <v>0.5533468354563774</v>
       </c>
     </row>
   </sheetData>
